--- a/it_forms/011_tech_data_protection_referral_form--it_forms.xlsx
+++ b/it_forms/011_tech_data_protection_referral_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -731,8 +731,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -760,12 +760,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'it_team_1'}</t>
+          <t>it_team_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'IT Team 1'}</t>
+          <t>IT Team 1</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'security_team'}</t>
+          <t>security_team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Security Team'}</t>
+          <t>Security Team</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'privacy_team'}</t>
+          <t>privacy_team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Privacy Team'}</t>
+          <t>Privacy Team</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'personal_data'}</t>
+          <t>personal_data</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Personal Data'}</t>
+          <t>Personal Data</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'technical_data'}</t>
+          <t>technical_data</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Technical Data'}</t>
+          <t>Technical Data</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'business_data'}</t>
+          <t>business_data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Business Data'}</t>
+          <t>Business Data</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'special_category_data'}</t>
+          <t>special_category_data</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Special Category Data'}</t>
+          <t>Special Category Data</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'confidential'}</t>
+          <t>confidential</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Confidential'}</t>
+          <t>Confidential</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'restricted'}</t>
+          <t>restricted</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Restricted'}</t>
+          <t>Restricted</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'not_resolved'}</t>
+          <t>not_resolved</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Not Resolved'}</t>
+          <t>Not Resolved</t>
         </is>
       </c>
     </row>
